--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="D8" t="n">
-        <v>27020</v>
+        <v>13510</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -650,51 +650,51 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仅买入未平仓 400股（跨期持有底仓）</t>
+          <t>仍买入未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>512760</v>
+        <v>300750</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>芯片ETF</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>14168</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>30400</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>561980</v>
+        <v>512760</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>芯片设备</t>
+          <t>芯片ETF</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20000</v>
+        <v>13000</v>
       </c>
       <c r="D10" t="n">
-        <v>13316</v>
+        <v>14168</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -704,24 +704,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅买入未平仓 20000股（跨期持有底仓）</t>
+          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>600498</v>
+        <v>561980</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>芯片设备</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>300</v>
+        <v>20000</v>
       </c>
       <c r="D11" t="n">
-        <v>12287</v>
+        <v>13316</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -731,24 +731,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>仅买入未平仓 300股（跨期持有底仓）</t>
+          <t>仅买入未平仓 20000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>601208</v>
+        <v>600498</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D12" t="n">
-        <v>4825.67</v>
+        <v>12287</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -758,24 +758,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仅买入未平仓 300股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>688008</v>
+        <v>601208</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>39060.43</v>
+        <v>4825.67</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -785,24 +785,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>仍买入未平仓 200股</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>688041</v>
+        <v>603228</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>景旺电子</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D14" t="n">
-        <v>50368</v>
+        <v>31566</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -812,32 +812,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>仅买入未平仓 300股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>688041</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>200</v>
+      </c>
+      <c r="D15" t="n">
+        <v>50368</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>688778</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>厦钨新能</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
         <v>500</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" t="n">
         <v>23195</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,18 +818,18 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>688041</v>
+        <v>688008</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>200</v>
       </c>
       <c r="D15" t="n">
-        <v>50368</v>
+        <v>39132.74</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -839,32 +839,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>仍买入未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>688041</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>200</v>
+      </c>
+      <c r="D16" t="n">
+        <v>50368</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>688778</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>厦钨新能</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
         <v>500</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F17" t="n">
         <v>23195</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -562,14 +562,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F5" t="n">
-        <v>3696.67</v>
+        <v>24401.25</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 100股</t>
+          <t>；仍卖出未平仓 600股</t>
         </is>
       </c>
     </row>
@@ -629,18 +629,18 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>300054</v>
+        <v>2916</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>鼎龙股份</t>
+          <t>深南电路</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>13510</v>
+        <v>38629</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -650,78 +650,78 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仍买入未平仓 200股</t>
+          <t>仅买入未平仓 100股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>300750</v>
+        <v>300054</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>鼎龙股份</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>13510</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>30400</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仍买入未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>512760</v>
+        <v>300750</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>芯片ETF</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>14168</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>30400</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>561980</v>
+        <v>512760</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>芯片设备</t>
+          <t>芯片ETF</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20000</v>
+        <v>13000</v>
       </c>
       <c r="D11" t="n">
-        <v>13316</v>
+        <v>14168</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -731,24 +731,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>仅买入未平仓 20000股（跨期持有底仓）</t>
+          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>600498</v>
+        <v>561980</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>芯片设备</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>300</v>
+        <v>20000</v>
       </c>
       <c r="D12" t="n">
-        <v>12287</v>
+        <v>13316</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -758,24 +758,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>仅买入未平仓 300股（跨期持有底仓）</t>
+          <t>仅买入未平仓 20000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>601208</v>
+        <v>600498</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D13" t="n">
-        <v>4825.67</v>
+        <v>12287</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -785,24 +785,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仅买入未平仓 300股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>603228</v>
+        <v>601208</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>景旺电子</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>31566</v>
+        <v>4825.67</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -812,24 +812,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>仅买入未平仓 300股（跨期持有底仓）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>688008</v>
+        <v>603228</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>景旺电子</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D15" t="n">
-        <v>39132.74</v>
+        <v>31566</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仍买入未平仓 200股</t>
+          <t>仅买入未平仓 300股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D16" t="n">
-        <v>50368</v>
+        <v>98680</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>仅买入未平仓 400股（跨期持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -466,8 +466,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>831</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -493,8 +495,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2156</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -520,8 +524,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2222</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -547,8 +553,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2436</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -574,8 +582,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2594</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -601,8 +611,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2837</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -628,8 +640,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2916</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>002916</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -655,8 +669,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>300054</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -682,8 +698,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>300750</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -709,8 +727,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>512760</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -736,8 +756,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>561980</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -763,8 +785,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>600498</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -790,8 +814,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>601208</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -817,8 +843,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>603228</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>603228</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -844,8 +872,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>688041</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -871,8 +901,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>688778</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>688778</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>

--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,14 +570,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="F5" t="n">
-        <v>24401.25</v>
+        <v>46276.15</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 600股</t>
+          <t>；仍卖出未平仓 1100股</t>
         </is>
       </c>
     </row>
@@ -700,48 +700,48 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>512760</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>芯片ETF</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>14168</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>30400</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>512760</t>
+          <t>561980</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>芯片ETF</t>
+          <t>芯片设备</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="D11" t="n">
-        <v>14168</v>
+        <v>6658</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -751,26 +751,26 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
+          <t>仍买入未平仓 10000股</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>561980</t>
+          <t>600498</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>芯片设备</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20000</v>
+        <v>300</v>
       </c>
       <c r="D12" t="n">
-        <v>13316</v>
+        <v>12287</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -780,26 +780,26 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>仅买入未平仓 20000股（跨期持有底仓）</t>
+          <t>仅买入未平仓 300股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>600498</t>
+          <t>601208</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>12287</v>
+        <v>4825.67</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -809,26 +809,26 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>仅买入未平仓 300股（跨期持有底仓）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>601208</t>
+          <t>603228</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>景旺电子</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D14" t="n">
-        <v>4825.67</v>
+        <v>31566</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -838,36 +838,36 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仅买入未平仓 300股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>603228</t>
+          <t>688008</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>景旺电子</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>31566</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>39907.5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仅买入未平仓 300股（跨期持有底仓）</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="D16" t="n">
-        <v>98680</v>
+        <v>49340</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -896,7 +896,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>仅买入未平仓 400股（跨期持有底仓）</t>
+          <t>仍买入未平仓 200股</t>
         </is>
       </c>
     </row>
@@ -926,6 +926,35 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>688820</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>盛合晶微</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>200</v>
+      </c>
+      <c r="D18" t="n">
+        <v>28090</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 200股（跨期持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,14 +570,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="F5" t="n">
-        <v>46276.15</v>
+        <v>37862.31</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 1100股</t>
+          <t>；仍卖出未平仓 900股</t>
         </is>
       </c>
     </row>
@@ -700,48 +700,48 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>512760</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>芯片ETF</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>14168</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>30330</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
+          <t>；仍卖出未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>561980</t>
+          <t>512760</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>芯片设备</t>
+          <t>芯片ETF</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="D11" t="n">
-        <v>6658</v>
+        <v>14168</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -751,26 +751,26 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>仍买入未平仓 10000股</t>
+          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>600498</t>
+          <t>561980</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>芯片设备</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>300</v>
+        <v>20000</v>
       </c>
       <c r="D12" t="n">
-        <v>12287</v>
+        <v>13504</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -780,26 +780,26 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>仅买入未平仓 300股（跨期持有底仓）</t>
+          <t>仍买入未平仓 20000股</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>601208</t>
+          <t>600127</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D13" t="n">
-        <v>4825.67</v>
+        <v>8015</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -809,26 +809,26 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仅买入未平仓 500股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>603228</t>
+          <t>600498</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>景旺电子</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>300</v>
       </c>
       <c r="D14" t="n">
-        <v>31566</v>
+        <v>12287</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -845,48 +845,48 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>688008</t>
+          <t>601208</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>4825.67</v>
       </c>
       <c r="E15" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>39907.5</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>603228</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>景旺电子</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D16" t="n">
-        <v>49340</v>
+        <v>42366</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -896,19 +896,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>仍买入未平仓 200股</t>
+          <t>仅买入未平仓 400股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>688778</t>
+          <t>688008</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>厦钨新能</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -918,33 +918,33 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F17" t="n">
-        <v>23195</v>
+        <v>39907.5</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>688820</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>盛合晶微</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>200</v>
       </c>
       <c r="D18" t="n">
-        <v>28090</v>
+        <v>49340</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -954,7 +954,152 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>仍买入未平仓 200股</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>迈威生物</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>500</v>
+      </c>
+      <c r="F19" t="n">
+        <v>13885</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>688127</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>蓝特光学</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>200</v>
+      </c>
+      <c r="D20" t="n">
+        <v>13902</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>仅买入未平仓 200股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>688603</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>天承科技</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>161</v>
+      </c>
+      <c r="D21" t="n">
+        <v>19704.79</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 161股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>688778</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>厦钨新能</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>500</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23195</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>688820</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>盛合晶微</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>400</v>
+      </c>
+      <c r="D23" t="n">
+        <v>55930</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 400股（跨期持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>6578.5</v>
+        <v>27330.4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仍买入未平仓 400股</t>
         </is>
       </c>
     </row>
@@ -570,14 +570,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="F5" t="n">
-        <v>37862.31</v>
+        <v>46858.53</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 900股</t>
+          <t>；仍卖出未平仓 1100股</t>
         </is>
       </c>
     </row>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="D7" t="n">
-        <v>38778</v>
+        <v>57129</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅买入未平仓 600股（跨期持有底仓）</t>
+          <t>仅买入未平仓 900股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -715,14 +715,14 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F10" t="n">
-        <v>30330</v>
+        <v>60433.33</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 100股</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
@@ -787,19 +787,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>600127</t>
+          <t>600498</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D13" t="n">
-        <v>8015</v>
+        <v>12287</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -809,26 +809,26 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>仅买入未平仓 500股（跨期持有底仓）</t>
+          <t>仅买入未平仓 300股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>600498</t>
+          <t>601208</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>12287</v>
+        <v>4825.67</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -838,26 +838,26 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>仅买入未平仓 300股（跨期持有底仓）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>601208</t>
+          <t>603228</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>景旺电子</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="D15" t="n">
-        <v>4825.67</v>
+        <v>64186</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -867,142 +867,142 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仅买入未平仓 600股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>603228</t>
+          <t>688008</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>景旺电子</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>42366</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>39907.5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>仅买入未平仓 400股（跨期持有底仓）</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>688008</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>49340</v>
       </c>
       <c r="E17" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>39907.5</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>仍买入未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>688062</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>迈威生物</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>49340</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>13885</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>仍买入未平仓 200股</t>
+          <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>688062</t>
+          <t>688127</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>迈威生物</t>
+          <t>蓝特光学</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>13902</v>
       </c>
       <c r="E19" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>13885</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 200股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>688127</t>
+          <t>688603</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>蓝特光学</t>
+          <t>天承科技</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D20" t="n">
-        <v>13902</v>
+        <v>12239</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1012,92 +1012,63 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>688603</t>
+          <t>688778</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>天承科技</t>
+          <t>厦钨新能</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>19704.79</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>23195</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>仅买入未平仓 161股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>688778</t>
+          <t>688820</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>厦钨新能</t>
+          <t>盛合晶微</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>55930</v>
       </c>
       <c r="E22" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>23195</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
-        <is>
-          <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>688820</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>盛合晶微</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>400</v>
-      </c>
-      <c r="D23" t="n">
-        <v>55930</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr">
         <is>
           <t>仅买入未平仓 400股（跨期持有底仓）</t>
         </is>

--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -570,14 +570,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="F5" t="n">
-        <v>46858.53</v>
+        <v>25559.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 1100股</t>
+          <t>；仍卖出未平仓 600股</t>
         </is>
       </c>
     </row>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D17" t="n">
-        <v>49340</v>
+        <v>98951.33</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -925,7 +925,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>仍买入未平仓 200股</t>
+          <t>仍买入未平仓 400股</t>
         </is>
       </c>
     </row>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="D19" t="n">
-        <v>13902</v>
+        <v>40542</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>仅买入未平仓 600股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D20" t="n">
-        <v>12239</v>
+        <v>24756.16</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仍买入未平仓 200股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="D19" t="n">
-        <v>40542</v>
+        <v>53122</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>仅买入未平仓 600股（跨期持有底仓）</t>
+          <t>仅买入未平仓 800股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D20" t="n">
-        <v>24756.16</v>
+        <v>48339.08</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>仍买入未平仓 200股</t>
+          <t>仍买入未平仓 400股</t>
         </is>
       </c>
     </row>
